--- a/Data/t13.2.xlsx
+++ b/Data/t13.2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2847,6 +2847,190 @@
         <v>20.5</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Agricultura, pecuária, produção florestal, pesca e aquicultura</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>113</v>
+      </c>
+      <c r="E106" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Indústria geral</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>81</v>
+      </c>
+      <c r="E107" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Construção</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>64</v>
+      </c>
+      <c r="E108" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Comércio, reparação de veículos automotores e motocicletas</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>205</v>
+      </c>
+      <c r="E109" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Transporte, armazenagem e correio</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>44</v>
+      </c>
+      <c r="E110" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Alojamento e alimentação</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>55</v>
+      </c>
+      <c r="E111" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Informação, comunicação e atividades financeiras, imobiliárias, profissionais e administrativas</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>99</v>
+      </c>
+      <c r="E112" t="n">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Administração pública, defesa, seguridade social, educação, saúde humana e serviços sociais</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>203</v>
+      </c>
+      <c r="E113" t="n">
+        <v>21.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
